--- a/output/pdf_financials_xlsx/LOVE.xlsx
+++ b/output/pdf_financials_xlsx/LOVE.xlsx
@@ -840,7 +840,7 @@
         <v>0.027088</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.683848</v>
+        <v>0.679615</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>-2.139985</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.655653</v>
+        <v>-13.65142</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>-2.139985</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.655653</v>
+        <v>-13.65142</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>12.899672</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>26.505992</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.771177</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>8.159305</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>12.114691</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.270517</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.620387</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>14.360016</v>
       </c>
     </row>
     <row r="35">
@@ -1747,28 +1747,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>12.899672</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>26.505992</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.771177</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>8.159305</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>12.114691</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.270517</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.620387</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>14.360016</v>
       </c>
     </row>
     <row r="37">
@@ -2125,22 +2125,22 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.323407</v>
+        <v>1.55223</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>10.842994</v>
+        <v>2.683689</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>19.194779</v>
+        <v>7.080088</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>13.105542</v>
+        <v>8.835025</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>21.013456</v>
+        <v>14.393069</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>23.53606</v>
+        <v>9.176043999999999</v>
       </c>
     </row>
     <row r="49">
@@ -4581,22 +4581,22 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.311773</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.313092</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-34</v>
+        <v>-34.299649</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>-1.965961</v>
+        <v>-0.274343</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.258608</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.347726</v>
       </c>
     </row>
     <row r="125">
@@ -4612,22 +4612,22 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.311773</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.313092</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-34</v>
+        <v>-34.299649</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>-1.965961</v>
+        <v>-0.274343</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.258608</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.347726</v>
       </c>
     </row>
     <row r="126">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -17886,7 +17886,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -19252,7 +19256,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -20390,7 +20398,11 @@
           <t>Lease payments (note 7)</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -21370,7 +21382,11 @@
           <t>Lease payments (note 7)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -22408,7 +22424,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -30972,7 +30992,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E483" s="5" t="n">

--- a/output/pdf_financials_xlsx/LOVE.xlsx
+++ b/output/pdf_financials_xlsx/LOVE.xlsx
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.295765</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.873345</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.139985</v>
+        <v>-1.84422</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.65142</v>
+        <v>-12.778075</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>6.352815</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.139985</v>
+        <v>-1.84422</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.65142</v>
+        <v>-12.778075</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>6.945418</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.438484</v>
+        <v>12.791299</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -3821,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.152144</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.158211</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.352815</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>6.684886</v>
       </c>
     </row>
     <row r="101">
@@ -4193,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.042955</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.217362</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -16610,7 +16610,11 @@
           <t>Depreciation of property, plant and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -16664,7 +16668,11 @@
           <t>Depreciation of right-of-use asset (note 8)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -21936,7 +21944,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -22652,7 +22660,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -31322,7 +31334,11 @@
           <t>Net finance expense $</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E489" s="5" t="n">
         <v>0.295765</v>
       </c>

--- a/output/pdf_financials_xlsx/LOVE.xlsx
+++ b/output/pdf_financials_xlsx/LOVE.xlsx
@@ -4007,22 +4007,22 @@
         <v>1.012057</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-1.116237</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-3.819797</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>-11.483197</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-5.639043</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-2.498514</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-6.304404</v>
       </c>
     </row>
     <row r="107">
@@ -6320,7 +6320,11 @@
           <t>Lease liabilities (note 8)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -10074,7 +10078,11 @@
           <t>Lease liabilities (note 7)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -17312,7 +17320,11 @@
           <t>Net change in non-cash operating working capital items (note 21)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -20132,7 +20144,11 @@
           <t>Net change in non-cash operating working capital items (note 20)</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -20796,7 +20812,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -22324,7 +22344,11 @@
           <t>Net change in non-cash operating working capital items (note 23)</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
